--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test-automation\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AAAD4-F33F-4783-9E13-FD24C0A5A03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A259FC8E-918C-457C-A390-B04E4842D883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="287">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -648,245 +648,2138 @@
     <t>Platform/App Names</t>
   </si>
   <si>
-    <t>"Facebook" – app name preserved.</t>
-  </si>
-  <si>
     <t>Question forms</t>
   </si>
   <si>
-    <t>Entire sentence is a conditional question form</t>
-  </si>
-  <si>
     <t>Inputs with Dates</t>
   </si>
   <si>
-    <t>"April 30" – month+date format.</t>
-  </si>
-  <si>
     <t>Inputs with Unit of Measurements</t>
   </si>
   <si>
-    <t>"kilomitara 5k" – unit + numeric suffix.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Greetings</t>
   </si>
   <si>
     <t>Greetings</t>
   </si>
   <si>
-    <t>Confusion between mahaprana 'භ' and alpaprana 'බ'.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Multi-Word English Phrases in Singlish</t>
   </si>
   <si>
     <t>Multi-Word English Phrases in Singlish</t>
   </si>
   <si>
-    <t>Phonetically transliterated phrase instead of preserving English script.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Isolated English Word Insertions in Singlish</t>
   </si>
   <si>
     <t>Isolated English Word Insertions in Singlish</t>
   </si>
   <si>
-    <t>Transliterated 'class' into Sinhala instead of keeping English script.</t>
-  </si>
-  <si>
     <t>Repeated Words</t>
   </si>
   <si>
-    <t>laga laga' repeated informal word tool එකට correctly transliterate කරන්න බැරිවෙනවා</t>
-  </si>
-  <si>
     <t>Responses</t>
   </si>
   <si>
-    <t>A short negative response saying 'No, I don't know'</t>
-  </si>
-  <si>
-    <t>A response expressing surprise and advising to be careful</t>
-  </si>
-  <si>
     <t>Inputs with Slang and Casual Phrasing</t>
   </si>
   <si>
-    <t>Long vowels in 'Ado' and 'Bande' missing in output.</t>
-  </si>
-  <si>
-    <t>Contains question word "kawadda" (කවද්ද) + question mark, follows informal Singlish question structure without auxiliary inversion</t>
-  </si>
-  <si>
     <t>Inputs with Punctuation Marks</t>
   </si>
   <si>
-    <t>Contains ellipsis (...) and question mark punctuation</t>
-  </si>
-  <si>
     <t>Romanization / Spelling Variants</t>
   </si>
   <si>
-    <t>mang' variant of 'mama/man', 'oyta' variant of 'oyata'</t>
-  </si>
-  <si>
     <t>English Digital Terms in Singlish</t>
   </si>
   <si>
-    <t>Digital terms 'screenshot' and 'zoom' used in Singlish context; comma needed mid-sentence for correct flow</t>
-  </si>
-  <si>
-    <t>English words 'morning', 'gym', 'breakfast' inserted individually in Singlish; 'eka kalin' = 'ඒකට කලින්' correct translation</t>
-  </si>
-  <si>
-    <t>Multi-word English phrase 'let me know if you're free' embedded in Singlish; 'api' = 'අපේ' (possessive), 'thiyanawa' = 'තියෙනවා'</t>
-  </si>
-  <si>
-    <t>"ah, ehemai" = agreement/response to prior statement.</t>
-  </si>
-  <si>
-    <t>Digital term 'Bluetooth' used in a Singlish sentence</t>
-  </si>
-  <si>
-    <t>"cm 10k" – measurement abbreviation + number.</t>
-  </si>
-  <si>
     <t>Platform/App Names in Singlish</t>
   </si>
   <si>
-    <t>Platform name 'TikTok' and digital term 'viral' combined with informal phrase 'kisi kenekuta' causes tool failure</t>
-  </si>
-  <si>
-    <t>Platform names 'Instagram' and 'Netflix' embedded in Singlish</t>
-  </si>
-  <si>
     <t>Inputs with Slang and Casual Phrasing; Multi-Word English Phrases in Singlish; Inputs with Punctuation Marks; Responses</t>
   </si>
   <si>
-    <t>Slang 'mara waste', multi-word English phrases 'deadline moved to next week', 'this is so frustrating', punctuation '!', '...', '?', 'ne?' = 'නේද?' response phrase</t>
-  </si>
-  <si>
     <t>English Abbreviations/Acronyms</t>
   </si>
   <si>
-    <t xml:space="preserve">	"ID" – common English abbreviation.</t>
-  </si>
-  <si>
-    <t>New Year greeting wishing everyone happiness</t>
-  </si>
-  <si>
     <t>English Clipped Forms</t>
   </si>
   <si>
-    <t>"exam" (from examination), "study" – clipped English words.</t>
-  </si>
-  <si>
     <t>Place Names Embedded in Singlish</t>
   </si>
   <si>
-    <t>Sri Lankan place name 'Kandy' embedded in Singlish question</t>
-  </si>
-  <si>
-    <t>"Kandy" – place name not translated.</t>
-  </si>
-  <si>
     <t>Person Names Embedded in Singlish</t>
   </si>
   <si>
-    <t>Sinhala person name 'Kasun' embedded in a Singlish sentence</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Requests</t>
   </si>
   <si>
-    <t>English request word 'please' (misspelled) converted to poor phonetic Sinhala.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	"Ranil" – person name without translation.</t>
-  </si>
-  <si>
-    <t>Kohomda' compressed spelling variant of 'kohomada', 'machan' casual slang, 'sandheepda' spelling variant of 'saneepada' — combination causes tool failure</t>
-  </si>
-  <si>
     <t>Inputs with Currency</t>
   </si>
   <si>
-    <t>"Rs. 1500" – Sri Lankan rupee symbol + amount.</t>
-  </si>
-  <si>
     <t>Inputs with Time Formats</t>
   </si>
   <si>
-    <t>"11:15PM" – time format with AM/PM</t>
-  </si>
-  <si>
-    <t>"12.30pm" – alternative time format.</t>
-  </si>
-  <si>
-    <t>Time formats '12:30' and '2:00PM' embedded in Singlish</t>
-  </si>
-  <si>
-    <t>Date 'June 5' embedded in Singlish sentence</t>
-  </si>
-  <si>
-    <t>ISO date format '2025-12-25' and month name 'Christmas' in Singlish</t>
-  </si>
-  <si>
-    <t>ymu' is a compressed variant of 'yamuda' and 'kohda' is a variant of 'koheda'</t>
-  </si>
-  <si>
-    <t>Unit 'metara' (meters) with numeric suffix '500k' in Singlish</t>
-  </si>
-  <si>
-    <t>Time indicator 'am' transliterated to Sinhala script.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Inputs with Time Formats</t>
   </si>
   <si>
-    <t>Digital terms 'router' and 'restart' should remain in English.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> English Digital Terms in Singlish</t>
   </si>
   <si>
     <t xml:space="preserve"> Platform/App Names in Singlish</t>
   </si>
   <si>
-    <t>Platform name failed to remain in English script.</t>
-  </si>
-  <si>
     <t>Online Indentifiers in Singlish</t>
   </si>
   <si>
-    <t>Email address 'saman@company.lk' and @mention '@Ruwan' in Singlish</t>
-  </si>
-  <si>
     <t>Inputs Containing Emojis</t>
   </si>
   <si>
-    <t>Emoji 😕 placed at the end of a Singlish sentence</t>
-  </si>
-  <si>
-    <t>Two emojis 🎉 and 🙏 placed mid-sentence and at end of Singlish</t>
-  </si>
-  <si>
-    <t>Contains yawning/bored emoji "🥱"</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Online Indentifiers in Singlish</t>
   </si>
   <si>
-    <t>URL 'google.com' transliterated to Sinhala script.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'April 30'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> month+date format.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'oya hetama enna...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Entire sentence is a conditional question form</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Facebook'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: app name preserved.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Subha dawasak w...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Confusion between mahaprana 'භ' and alpaprana 'බ'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'mama den very b...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Phonetically transliterated phrase instead of preserving English script.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'ada class ekak ...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Transliterated 'class' into Sinhala instead of keeping English script.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Laga laga ennam...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> laga laga' repeated informal word tool එකට correctly transliterate කරන්න බැරිවෙනවා</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">'Nehe, mama dann...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: A short negative response saying 'No, I don't know'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Ahh, mama hithu...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: A response expressing surprise and advising to be careful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Ado maru bande....'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Long vowels in 'Ado' and 'Bande' missing in output.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 'kilomitara 5k'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: unit + numeric suffix.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'kawadda'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (කවද්ද) + question mark, follows informal Singlish question structure without auxiliary inversion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 'ada class ekak ...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: Transliterated 'class' into Sinhala instead of keeping English script.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Mama hithanawa....'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Contains ellipsis (...) and question mark punctuation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'mama den very b...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Phonetically transliterated phrase instead of preserving English script.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'mang oyta kiwwe...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mang' variant of 'mama/man', 'oyta' variant of 'oyata'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'mama'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Digital terms 'screenshot' and 'zoom' used in Singlish context; comma needed mid-sentence for correct flow</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'mama heta morni...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: English words 'morning', 'gym', 'breakfast' inserted individually in Singlish; 'eka kalin' = 'ඒකට කලින්' correct translation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'mama api weeken...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Multi-word English phrase 'let me know if you're free' embedded in Singlish; 'api' = 'අපේ' (possessive), 'thiyanawa' = 'තියෙනවා'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'ah, ehemai'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = agreement/response to prior statement.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'oya'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Digital term 'Bluetooth' used in a Singlish sentence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'cm 10k'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: measurement abbreviation + number.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'TikTok'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Platform name 'TikTok' and digital term 'viral' combined with informal phrase 'kisi kenekuta' causes tool failure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Oya'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Platform names 'Instagram' and 'Netflix' embedded in Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Bro, ada mara w...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Slang 'mara waste', multi-word English phrases 'deadline moved to next week', 'this is so frustrating', punctuation '!', '...', '?', 'ne?' = 'නේද?' response phrase</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'ID'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> common English abbreviation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Subha Aluth Avu...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: New Year greeting wishing everyone happiness</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'exam'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: (from examination), study – clipped English words.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Kandy'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sri Lankan place name 'Kandy' embedded in Singlish question</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Kandy'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: place name not translated.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Kasun'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Sinhala person name 'Kasun' embedded in a Singlish sentence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'eka mata denawa...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: English request word 'please' (misspelled) converted to poor phonetic Sinhala.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Ranil'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>person name without translation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Kohomda machan,...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Kohomda' compressed spelling variant of 'kohomada', 'machan' casual slang, 'sandheepda' spelling variant of 'saneepada' — combination causes tool failure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'Rs. 1500'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Sri Lankan rupee symbol + amount.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '11:15PM'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: time format with AM/PM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: '12.30pm'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: alternative time format.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'api noon 12:30 ...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Time formats '12:30' and '2:00PM' embedded in Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'heta June 5 wed...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Date 'June 5' embedded in Singlish sentence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: '2025-12-25 wala...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ISO date format '2025-12-25' and month name 'Christmas' in Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Apa adha ymu ko...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: ymu' is a compressed variant of 'yamuda' and 'kohda' is a variant of 'koheda'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'metara 500k wit...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Unit 'metara' (meters) with numeric suffix '500k' in Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '10:30am wenakan...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Time indicator 'am' transliterated to Sinhala script..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'router'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Digital terms 'router' and 'restart' should remain in English.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'instagram'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Platform name failed to remain in English script..</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'mata invoice ek...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Email address 'saman@company.lk' and @mention '@Ruwan' in Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: 'Oya awada, mama...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Emoji 😕 placed at the end of a Singlish sentence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'api heta trip e...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: Two emojis 🎉 and 🙏 placed mid-sentence and at end of Singlish</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 'meeka check kar...'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> URL 'google.com' transliterated to Sinhala script.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evidence: 🥱
+Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Iskoola Pota"/>
+        <family val="2"/>
+      </rPr>
+      <t>: "An emoji representing a yawn is used at the end of the sentence."</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,6 +2809,26 @@
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Iskoola Pota"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -963,7 +2876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1000,6 +2913,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1345,7 +3261,7 @@
         <v>206</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1368,10 +3284,10 @@
         <v>11</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1394,10 +3310,10 @@
         <v>11</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1420,10 +3336,10 @@
         <v>11</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>213</v>
+        <v>209</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1446,10 +3362,10 @@
         <v>11</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1472,10 +3388,10 @@
         <v>11</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1498,10 +3414,10 @@
         <v>11</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1524,10 +3440,10 @@
         <v>11</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1550,10 +3466,10 @@
         <v>11</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1576,10 +3492,10 @@
         <v>11</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1602,10 +3518,10 @@
         <v>11</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1628,10 +3544,10 @@
         <v>11</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1654,10 +3570,10 @@
         <v>11</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>222</v>
+        <v>214</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1680,10 +3596,10 @@
         <v>11</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1706,10 +3622,10 @@
         <v>11</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1732,10 +3648,10 @@
         <v>11</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,10 +3674,10 @@
         <v>11</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1784,10 +3700,10 @@
         <v>11</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1810,10 +3726,10 @@
         <v>11</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1836,10 +3752,10 @@
         <v>11</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1862,10 +3778,10 @@
         <v>11</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1888,10 +3804,10 @@
         <v>11</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1914,10 +3830,10 @@
         <v>11</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1940,10 +3856,10 @@
         <v>11</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1966,10 +3882,10 @@
         <v>11</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1992,10 +3908,10 @@
         <v>11</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2018,10 +3934,10 @@
         <v>11</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2044,10 +3960,10 @@
         <v>11</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2070,10 +3986,10 @@
         <v>11</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2096,10 +4012,10 @@
         <v>11</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2122,10 +4038,10 @@
         <v>11</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2148,10 +4064,10 @@
         <v>11</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2174,10 +4090,10 @@
         <v>11</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2200,10 +4116,10 @@
         <v>11</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2226,10 +4142,10 @@
         <v>11</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2252,10 +4168,10 @@
         <v>11</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2278,10 +4194,10 @@
         <v>11</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2304,10 +4220,10 @@
         <v>11</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2330,10 +4246,10 @@
         <v>11</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2356,10 +4272,10 @@
         <v>11</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2382,10 +4298,10 @@
         <v>11</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2408,10 +4324,10 @@
         <v>11</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2434,10 +4350,10 @@
         <v>11</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2460,10 +4376,10 @@
         <v>11</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>274</v>
+        <v>232</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2486,10 +4402,10 @@
         <v>11</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2512,10 +4428,10 @@
         <v>11</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2538,10 +4454,10 @@
         <v>11</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2564,10 +4480,10 @@
         <v>11</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2590,10 +4506,10 @@
         <v>11</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2616,10 +4532,10 @@
         <v>11</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
